--- a/GATEWAY/A1111SMESSRLXX/SMES_srl/XMED/4.0.0/report-checklist.xlsx
+++ b/GATEWAY/A1111SMESSRLXX/SMES_srl/XMED/4.0.0/report-checklist.xlsx
@@ -23,8 +23,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="d/m/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="16">
     <font>
@@ -490,7 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -676,6 +678,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2672,22 +2680,22 @@
 Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
         </is>
       </c>
-      <c r="F12" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G12" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F12" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G12" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H12" s="60" t="inlineStr">
         <is>
           <t>e2177037d1f2ff7b9dba14be463bf543</t>
         </is>
       </c>
-      <c r="I12" s="61" t="inlineStr"/>
+      <c r="I12" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J12" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2775,22 +2783,22 @@
 Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
         </is>
       </c>
-      <c r="F13" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G13" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F13" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G13" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H13" s="60" t="inlineStr">
         <is>
           <t>c3d66fc598eb614ef7cab45374821c2d</t>
         </is>
       </c>
-      <c r="I13" s="61" t="inlineStr"/>
+      <c r="I13" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J13" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -2929,22 +2937,22 @@
 Al fine di rendere non valido il token è necessario non valorizzare nel JWT il campo "purpose_of_use".</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F15" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G15" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H15" s="60" t="inlineStr">
         <is>
           <t>85220b8bdfdb5b27277974c25ae2dd00</t>
         </is>
       </c>
-      <c r="I15" s="61" t="inlineStr"/>
+      <c r="I15" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J15" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3236,22 +3244,22 @@
 Al fine di rendere non valido il token è necessario valorizzare il campo "action_id" con la stringa "TEST" (valore non ammesso).</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G20" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F20" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G20" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H20" s="60" t="inlineStr">
         <is>
           <t>1ddbe8b8b1ceef6e9f66dd527d4d67e2</t>
         </is>
       </c>
-      <c r="I20" s="61" t="inlineStr"/>
+      <c r="I20" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J20" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3339,22 +3347,22 @@
 Al fine di rendere non valido il token è necessario valorizzare il campo "action_id" con la stringa "TEST" (valore non ammesso).</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G21" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F21" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G21" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H21" s="60" t="inlineStr">
         <is>
           <t>43395eab0b6cc99ea3942960c14de63e</t>
         </is>
       </c>
-      <c r="I21" s="61" t="inlineStr"/>
+      <c r="I21" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J21" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3493,22 +3501,22 @@
 Al fine di rendere non valido il token è necessario valorizzare il campo "action_id" con la stringa "TEST" (valore non ammesso).</t>
         </is>
       </c>
-      <c r="F23" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G23" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T19:47:49Z</t>
-        </is>
+      <c r="F23" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G23" s="60" t="n">
+        <v>46092.82487268518</v>
       </c>
       <c r="H23" s="60" t="inlineStr">
         <is>
           <t>a2feae1dcf2bf3af51a9d07e89fdd6db</t>
         </is>
       </c>
-      <c r="I23" s="61" t="inlineStr"/>
+      <c r="I23" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J23" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3798,14 +3806,22 @@
 "ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
         </is>
       </c>
-      <c r="F28" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G28" s="60" t="n"/>
-      <c r="H28" s="60" t="n"/>
-      <c r="I28" s="61" t="n"/>
+      <c r="F28" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G28" s="60" t="n">
+        <v>46092.83333333334</v>
+      </c>
+      <c r="H28" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J28" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -3890,14 +3906,22 @@
 "ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
         </is>
       </c>
-      <c r="F29" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G29" s="60" t="n"/>
-      <c r="H29" s="60" t="n"/>
-      <c r="I29" s="61" t="n"/>
+      <c r="F29" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G29" s="60" t="n">
+        <v>46092.83333333334</v>
+      </c>
+      <c r="H29" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I29" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J29" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4034,14 +4058,22 @@
 "ERRORE BLOCCANTE (SI/NO)", "ERRORE VISIBILE A UTENTE (SI/NO)", "MESSAGGIO DI ERRORE", "GESTITO IN BACKOFFICE (SI/NO)", " PRESENTE CODA DI RETRY AUTOMATICA PER L'INVIO DEL DOCUMENTO AL FSE SERVIZIO DI VALIDAZIONE DEL GATEWAY A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)",  "INVIO MANUALE DEL DOCUMENTO AL FSE A SEGUITO DELLA RISOLUZIONE DELL'ERRORE (SI/NO)", "GESTIONE ERRORE".</t>
         </is>
       </c>
-      <c r="F31" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G31" s="60" t="n"/>
-      <c r="H31" s="60" t="n"/>
-      <c r="I31" s="61" t="n"/>
+      <c r="F31" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G31" s="60" t="n">
+        <v>46092.83333333334</v>
+      </c>
+      <c r="H31" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I31" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J31" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4666,22 +4698,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F43" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G43" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F43" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G43" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H43" s="60" t="inlineStr">
         <is>
           <t>efab6e7d2a7e070440dafd3390579087</t>
         </is>
       </c>
-      <c r="I43" s="61" t="inlineStr"/>
+      <c r="I43" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J43" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4766,18 +4798,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F44" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G44" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="H44" s="60" t="inlineStr"/>
-      <c r="I44" s="61" t="inlineStr"/>
+      <c r="F44" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G44" s="60" t="n">
+        <v>46092.83333333334</v>
+      </c>
+      <c r="H44" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J44" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4862,22 +4898,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F45" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G45" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F45" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G45" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H45" s="60" t="inlineStr">
         <is>
           <t>dc10d5f8cb6dc37db6590bc694c8fd91</t>
         </is>
       </c>
-      <c r="I45" s="61" t="inlineStr"/>
+      <c r="I45" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J45" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -4962,22 +4998,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F46" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G46" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F46" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G46" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H46" s="60" t="inlineStr">
         <is>
           <t>57a415ba147266bb546171261ae18840</t>
         </is>
       </c>
-      <c r="I46" s="61" t="inlineStr"/>
+      <c r="I46" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J46" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5062,22 +5098,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 11" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F47" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G47" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F47" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G47" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H47" s="60" t="inlineStr">
         <is>
           <t>07dbed9eded8d7c2b9e109836a799162</t>
         </is>
       </c>
-      <c r="I47" s="61" t="inlineStr"/>
+      <c r="I47" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J47" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5162,22 +5198,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 12" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F48" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G48" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F48" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G48" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H48" s="60" t="inlineStr">
         <is>
           <t>e76715746173568d0d44bef49b814709</t>
         </is>
       </c>
-      <c r="I48" s="61" t="inlineStr"/>
+      <c r="I48" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J48" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5262,22 +5298,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F49" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G49" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F49" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G49" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H49" s="60" t="inlineStr">
         <is>
           <t>1ddbe8b8b1ceef6e9f66dd527d4d67e2</t>
         </is>
       </c>
-      <c r="I49" s="61" t="inlineStr"/>
+      <c r="I49" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J49" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5362,22 +5398,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F50" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G50" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F50" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G50" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H50" s="60" t="inlineStr">
         <is>
           <t>43395eab0b6cc99ea3942960c14de63e</t>
         </is>
       </c>
-      <c r="I50" s="61" t="inlineStr"/>
+      <c r="I50" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J50" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5462,18 +5498,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F51" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G51" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
-      </c>
-      <c r="H51" s="60" t="inlineStr"/>
-      <c r="I51" s="61" t="inlineStr"/>
+      <c r="F51" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G51" s="60" t="n">
+        <v>46092.83333333334</v>
+      </c>
+      <c r="H51" s="60" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J51" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -5558,22 +5598,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F52" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G52" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F52" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G52" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H52" s="60" t="inlineStr">
         <is>
           <t>a2feae1dcf2bf3af51a9d07e89fdd6db</t>
         </is>
       </c>
-      <c r="I52" s="61" t="inlineStr"/>
+      <c r="I52" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J52" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8682,22 +8722,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F116" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G116" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F116" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G116" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H116" s="60" t="inlineStr">
         <is>
           <t>4901acd9605837d3d6adbd1d7e48dea7</t>
         </is>
       </c>
-      <c r="I116" s="61" t="inlineStr"/>
+      <c r="I116" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J116" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8782,22 +8822,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F117" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G117" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F117" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G117" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H117" s="60" t="inlineStr">
         <is>
           <t>aa9df56838617d4ffd35c1958ca309d7</t>
         </is>
       </c>
-      <c r="I117" s="61" t="inlineStr"/>
+      <c r="I117" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J117" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8882,22 +8922,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F118" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G118" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F118" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G118" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H118" s="60" t="inlineStr">
         <is>
           <t>2c649f34bdb8f065aeda381fb86a12d4</t>
         </is>
       </c>
-      <c r="I118" s="61" t="inlineStr"/>
+      <c r="I118" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J118" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -8982,22 +9022,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F119" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G119" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F119" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G119" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H119" s="60" t="inlineStr">
         <is>
           <t>65db572bb931c9598ece711942ac7c2f</t>
         </is>
       </c>
-      <c r="I119" s="61" t="inlineStr"/>
+      <c r="I119" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J119" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9082,22 +9122,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F120" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G120" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F120" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G120" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H120" s="60" t="inlineStr">
         <is>
           <t>2b299fe0307e61d1feac54dfab15747d</t>
         </is>
       </c>
-      <c r="I120" s="61" t="inlineStr"/>
+      <c r="I120" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J120" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9182,22 +9222,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F121" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G121" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F121" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G121" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H121" s="60" t="inlineStr">
         <is>
           <t>84b20e776ff38b4bfcf36db5f1cc60cd</t>
         </is>
       </c>
-      <c r="I121" s="61" t="inlineStr"/>
+      <c r="I121" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J121" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9282,22 +9322,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F122" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G122" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F122" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G122" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H122" s="60" t="inlineStr">
         <is>
           <t>862e5dc268978e8fbf0440ccc7a6d596</t>
         </is>
       </c>
-      <c r="I122" s="61" t="inlineStr"/>
+      <c r="I122" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J122" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9382,22 +9422,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F123" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G123" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F123" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G123" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H123" s="60" t="inlineStr">
         <is>
           <t>a7407b86203933c144c99c25ae096306</t>
         </is>
       </c>
-      <c r="I123" s="61" t="inlineStr"/>
+      <c r="I123" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J123" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9482,22 +9522,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F124" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G124" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F124" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G124" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H124" s="60" t="inlineStr">
         <is>
           <t>9f1e6165aa15af67cfcdaf553b2d31e9</t>
         </is>
       </c>
-      <c r="I124" s="61" t="inlineStr"/>
+      <c r="I124" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J124" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9582,22 +9622,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F125" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G125" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F125" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G125" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H125" s="60" t="inlineStr">
         <is>
           <t>7108493bebdeff5428a5d632685fd259</t>
         </is>
       </c>
-      <c r="I125" s="61" t="inlineStr"/>
+      <c r="I125" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J125" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9682,22 +9722,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F126" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G126" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F126" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G126" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H126" s="60" t="inlineStr">
         <is>
           <t>a523de18a28e816b86f9d9b38ce9fe8f</t>
         </is>
       </c>
-      <c r="I126" s="61" t="inlineStr"/>
+      <c r="I126" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J126" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9782,22 +9822,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F127" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G127" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F127" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G127" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H127" s="60" t="inlineStr">
         <is>
           <t>61e43f7b5186b2cf227c0d40f3b157f1</t>
         </is>
       </c>
-      <c r="I127" s="61" t="inlineStr"/>
+      <c r="I127" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J127" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9882,22 +9922,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F128" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G128" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F128" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G128" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H128" s="60" t="inlineStr">
         <is>
           <t>bc183e112b5e2b3ade84013203f39fcb</t>
         </is>
       </c>
-      <c r="I128" s="61" t="inlineStr"/>
+      <c r="I128" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J128" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -9982,22 +10022,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F129" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G129" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F129" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G129" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H129" s="60" t="inlineStr">
         <is>
           <t>237c69165088035be07e005eeb4a7225</t>
         </is>
       </c>
-      <c r="I129" s="61" t="inlineStr"/>
+      <c r="I129" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J129" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10082,22 +10122,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 23" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F130" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G130" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F130" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G130" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H130" s="60" t="inlineStr">
         <is>
           <t>9bc42f098ac64bc01aa36e93aadad125</t>
         </is>
       </c>
-      <c r="I130" s="61" t="inlineStr"/>
+      <c r="I130" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J130" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10182,22 +10222,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 6" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F131" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G131" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F131" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G131" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H131" s="60" t="inlineStr">
         <is>
           <t>c21987da5a49b336f64a3964f4c94a21</t>
         </is>
       </c>
-      <c r="I131" s="61" t="inlineStr"/>
+      <c r="I131" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J131" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10282,22 +10322,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 8" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F132" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G132" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F132" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G132" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H132" s="60" t="inlineStr">
         <is>
           <t>ae3bbe54b31ca50bd4b16b912c164618</t>
         </is>
       </c>
-      <c r="I132" s="61" t="inlineStr"/>
+      <c r="I132" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J132" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10382,22 +10422,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 9" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F133" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G133" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F133" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G133" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H133" s="60" t="inlineStr">
         <is>
           <t>e376adc08a2f785b0d77fbeea766da8d</t>
         </is>
       </c>
-      <c r="I133" s="61" t="inlineStr"/>
+      <c r="I133" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J133" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10482,22 +10522,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 10" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F134" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G134" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F134" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G134" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H134" s="60" t="inlineStr">
         <is>
           <t>70f69074a8d454c240f2fef48e604800</t>
         </is>
       </c>
-      <c r="I134" s="61" t="inlineStr"/>
+      <c r="I134" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J134" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10582,22 +10622,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 11" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F135" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G135" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F135" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G135" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H135" s="60" t="inlineStr">
         <is>
           <t>ee970f7a60acd9d460a85ff291ce8f82</t>
         </is>
       </c>
-      <c r="I135" s="61" t="inlineStr"/>
+      <c r="I135" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J135" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10682,22 +10722,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 12" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F136" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G136" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F136" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G136" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H136" s="60" t="inlineStr">
         <is>
           <t>7f901016432badbbd165ec90bd42c804</t>
         </is>
       </c>
-      <c r="I136" s="61" t="inlineStr"/>
+      <c r="I136" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J136" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10782,22 +10822,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 13" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F137" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G137" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F137" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G137" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H137" s="60" t="inlineStr">
         <is>
           <t>e7576f68108fa4f3512330557f4a3845</t>
         </is>
       </c>
-      <c r="I137" s="61" t="inlineStr"/>
+      <c r="I137" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J137" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10882,22 +10922,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 14" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F138" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G138" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F138" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G138" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H138" s="60" t="inlineStr">
         <is>
           <t>02151a6a213c2c3f23c525d56f99b738</t>
         </is>
       </c>
-      <c r="I138" s="61" t="inlineStr"/>
+      <c r="I138" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J138" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -10982,22 +11022,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 15" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F139" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G139" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F139" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G139" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H139" s="60" t="inlineStr">
         <is>
           <t>0e9a518b29619c25556490242c3d0ad6</t>
         </is>
       </c>
-      <c r="I139" s="61" t="inlineStr"/>
+      <c r="I139" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J139" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11082,22 +11122,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 16" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F140" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G140" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F140" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G140" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H140" s="60" t="inlineStr">
         <is>
           <t>6cf583b7d1d2e53af0fd327b50eed239</t>
         </is>
       </c>
-      <c r="I140" s="61" t="inlineStr"/>
+      <c r="I140" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J140" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11182,22 +11222,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 17" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F141" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G141" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F141" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G141" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H141" s="60" t="inlineStr">
         <is>
           <t>95ad73b4200a0b227d5efe5bfa3452e3</t>
         </is>
       </c>
-      <c r="I141" s="61" t="inlineStr"/>
+      <c r="I141" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J141" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11282,22 +11322,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 18" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F142" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G142" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F142" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G142" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H142" s="60" t="inlineStr">
         <is>
           <t>67ca96c09a4ab3dd925b5e06f590b779</t>
         </is>
       </c>
-      <c r="I142" s="61" t="inlineStr"/>
+      <c r="I142" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J142" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11382,22 +11422,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 19" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F143" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G143" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F143" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G143" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H143" s="60" t="inlineStr">
         <is>
           <t>5f40bc897fec4e5b6aa6869cb4cc9771</t>
         </is>
       </c>
-      <c r="I143" s="61" t="inlineStr"/>
+      <c r="I143" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J143" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11482,22 +11522,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F144" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G144" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F144" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G144" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H144" s="60" t="inlineStr">
         <is>
           <t>48c9699cb8404dbccc4f614f090f053e</t>
         </is>
       </c>
-      <c r="I144" s="61" t="inlineStr"/>
+      <c r="I144" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J144" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -11582,22 +11622,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 21" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F145" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G145" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F145" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G145" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H145" s="60" t="inlineStr">
         <is>
           <t>c4b2b88fd4138e24cc916ac15a0bc590</t>
         </is>
       </c>
-      <c r="I145" s="61" t="inlineStr"/>
+      <c r="I145" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J145" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -12560,15 +12600,11 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 24" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F164" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G164" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F164" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G164" s="60" t="n">
+        <v>46092.7530787037</v>
       </c>
       <c r="H164" s="60" t="inlineStr">
         <is>
@@ -12577,7 +12613,7 @@
       </c>
       <c r="I164" s="61" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78816ff9ce12</t>
+          <t>2.16.840.1.113883.2.9.2.120.4.4.2149fb78666c205ac20b9bd2d882af037f0819429c691196eaa8054488c56c20.816ff9ce12^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
         </is>
       </c>
       <c r="J164" s="62" t="inlineStr">
@@ -12597,7 +12633,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O164" s="62" t="inlineStr"/>
+      <c r="O164" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P164" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -12660,15 +12700,11 @@
 Il Documento CDA2 Referto Specialistica Ambulatoriale dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 25" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F165" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G165" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F165" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G165" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H165" s="60" t="inlineStr">
         <is>
@@ -12697,7 +12733,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O165" s="62" t="inlineStr"/>
+      <c r="O165" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P165" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -12760,15 +12800,11 @@
 Il Documento CDA2 Lettera Dimissione Ospedaliera dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 17" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F166" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G166" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F166" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G166" s="60" t="n">
+        <v>46092.7530787037</v>
       </c>
       <c r="H166" s="60" t="inlineStr">
         <is>
@@ -12777,7 +12813,7 @@
       </c>
       <c r="I166" s="61" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df02d7d44ab8c</t>
+          <t>2.16.840.1.113883.2.9.2.120.4.4.46a41df0ab0514f11c0811056832c3225e06c8e11824f27c7e5517ca5cfc57fe.2d7d44ab8c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
         </is>
       </c>
       <c r="J166" s="62" t="inlineStr">
@@ -12797,7 +12833,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O166" s="62" t="inlineStr"/>
+      <c r="O166" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P166" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -12860,15 +12900,11 @@
 Il Documento CDA2 Lettera Dimissione Ospedaliera dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso dalla sezione "CASO DI TEST 18" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_OK" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F167" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G167" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F167" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G167" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H167" s="60" t="inlineStr">
         <is>
@@ -12897,7 +12933,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O167" s="62" t="inlineStr"/>
+      <c r="O167" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P167" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -13345,22 +13385,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 26" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F176" s="57" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G176" s="57" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F176" s="75" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G176" s="76" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H176" s="57" t="inlineStr">
         <is>
           <t>c89f3cf9745f679924a156f94e9ae2da</t>
         </is>
       </c>
-      <c r="I176" s="57" t="inlineStr"/>
+      <c r="I176" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J176" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13685,22 +13725,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 20" riportata nei documenti "casi di test LDO" e "CDA2_Lettera di Dimissione Ospedaliera_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento. </t>
         </is>
       </c>
-      <c r="F182" s="57" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G182" s="57" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F182" s="75" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G182" s="76" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H182" s="57" t="inlineStr">
         <is>
           <t>1a3af89e05489d79d83f57ef42b0f293</t>
         </is>
       </c>
-      <c r="I182" s="57" t="inlineStr"/>
+      <c r="I182" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J182" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13785,22 +13825,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 27" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F183" s="57" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G183" s="57" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F183" s="75" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G183" s="76" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H183" s="57" t="inlineStr">
         <is>
           <t>bda70a2757814ff47064a61313d32181</t>
         </is>
       </c>
-      <c r="I183" s="57" t="inlineStr"/>
+      <c r="I183" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J183" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -13885,22 +13925,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 22" riportata nei documenti "casi di test PSS" e "CDA2_Profilo_Sanitario_Sintetico_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F184" s="57" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G184" s="57" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F184" s="75" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G184" s="76" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H184" s="57" t="inlineStr">
         <is>
           <t>553beb3a86d37830c44f5b1dd7dbbce0</t>
         </is>
       </c>
-      <c r="I184" s="57" t="inlineStr"/>
+      <c r="I184" s="57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J184" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14225,22 +14265,22 @@
 I dati utilizzati per comporre il CDA2 dovranno essere conformi alle section e le entry secondo quanto espresso nella sezione "CASO DI TEST 28" riportata nei documenti "casi di test RSA" e "CDA2_Referto_Specialistica_Ambulatoriale_KO" presenti al path https://github.com/ministero-salute/it-fse-accreditamento.</t>
         </is>
       </c>
-      <c r="F190" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G190" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F190" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G190" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H190" s="60" t="inlineStr">
         <is>
           <t>f6761942ebd38f94f0492724366db68b</t>
         </is>
       </c>
-      <c r="I190" s="61" t="inlineStr"/>
+      <c r="I190" s="61" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="J190" s="62" t="inlineStr">
         <is>
           <t>SI</t>
@@ -14326,15 +14366,11 @@
 </t>
         </is>
       </c>
-      <c r="F191" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G191" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F191" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G191" s="60" t="n">
+        <v>46092.7530787037</v>
       </c>
       <c r="H191" s="60" t="inlineStr">
         <is>
@@ -14343,7 +14379,7 @@
       </c>
       <c r="I191" s="61" t="inlineStr">
         <is>
-          <t>2.16.840.1.113883.2.9.2.120.4.4.a9f4347f06017338d2</t>
+          <t>2.16.840.1.113883.2.9.2.120.4.4.a9f4347f79cf3e1cf2ff4d79eaf6d0cf8d4a82cf3fb4e942adcc54e7fc27772e.06017338d2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
         </is>
       </c>
       <c r="J191" s="62" t="inlineStr">
@@ -14363,7 +14399,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O191" s="62" t="inlineStr"/>
+      <c r="O191" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P191" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -14427,15 +14467,11 @@
 </t>
         </is>
       </c>
-      <c r="F192" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G192" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F192" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G192" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H192" s="60" t="inlineStr">
         <is>
@@ -14464,7 +14500,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O192" s="62" t="inlineStr"/>
+      <c r="O192" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P192" s="62" t="inlineStr">
         <is>
           <t>NO</t>
@@ -14527,15 +14567,11 @@
 Il Documento CDA2 Profilo Sanitario Sintetico dovrà essere composto in modo da risultare valido dal punto di vista sintattico, semantico, terminologico. Il "CASO DI TEST 25" si riferisce a un esempio di CDA2 semplice, contenente esclusivamente sezioni ed elementi obbligatori previsti dalle specifiche nazionali (IG HL7 Italia)</t>
         </is>
       </c>
-      <c r="F193" s="60" t="inlineStr">
-        <is>
-          <t>11/03/2026</t>
-        </is>
-      </c>
-      <c r="G193" s="60" t="inlineStr">
-        <is>
-          <t>2026-03-11T20:00:00Z</t>
-        </is>
+      <c r="F193" s="60" t="n">
+        <v>46092</v>
+      </c>
+      <c r="G193" s="60" t="n">
+        <v>46092.83333333334</v>
       </c>
       <c r="H193" s="60" t="inlineStr">
         <is>
@@ -14564,7 +14600,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="O193" s="62" t="inlineStr"/>
+      <c r="O193" s="62" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="P193" s="62" t="inlineStr">
         <is>
           <t>NO</t>
